--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>121407557</v>
       </c>
       <c r="B2" t="n">
-        <v>91247</v>
+        <v>91259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,6 +782,339 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121498378</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90730</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rotetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>621889</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6525447</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Noterad</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Grusell, Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121498382</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90730</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rotetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>621850</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6525430</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Noterad</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Grusell, Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121498381</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90730</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rotetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>621849</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6525428</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Noterad</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Grusell, Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121407557</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>91260</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498378</v>
+        <v>121498382</v>
       </c>
       <c r="B3" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621889</v>
+        <v>621850</v>
       </c>
       <c r="R3" t="n">
-        <v>6525447</v>
+        <v>6525430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498382</v>
+        <v>121498381</v>
       </c>
       <c r="B4" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621850</v>
+        <v>621849</v>
       </c>
       <c r="R4" t="n">
-        <v>6525430</v>
+        <v>6525428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498381</v>
+        <v>121498378</v>
       </c>
       <c r="B5" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621849</v>
+        <v>621889</v>
       </c>
       <c r="R5" t="n">
-        <v>6525428</v>
+        <v>6525447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121407557</v>
       </c>
       <c r="B2" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498382</v>
+        <v>121498378</v>
       </c>
       <c r="B3" t="n">
         <v>90733</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621850</v>
+        <v>621889</v>
       </c>
       <c r="R3" t="n">
-        <v>6525430</v>
+        <v>6525447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498378</v>
+        <v>121498382</v>
       </c>
       <c r="B5" t="n">
         <v>90733</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621889</v>
+        <v>621850</v>
       </c>
       <c r="R5" t="n">
-        <v>6525447</v>
+        <v>6525430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498381</v>
+        <v>121498382</v>
       </c>
       <c r="B4" t="n">
         <v>90733</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621849</v>
+        <v>621850</v>
       </c>
       <c r="R4" t="n">
-        <v>6525428</v>
+        <v>6525430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498382</v>
+        <v>121498381</v>
       </c>
       <c r="B5" t="n">
         <v>90733</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621850</v>
+        <v>621849</v>
       </c>
       <c r="R5" t="n">
-        <v>6525430</v>
+        <v>6525428</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121407557</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>91269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121498378</v>
       </c>
       <c r="B3" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498382</v>
+        <v>121498381</v>
       </c>
       <c r="B4" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621850</v>
+        <v>621849</v>
       </c>
       <c r="R4" t="n">
-        <v>6525430</v>
+        <v>6525428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498381</v>
+        <v>121498382</v>
       </c>
       <c r="B5" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621849</v>
+        <v>621850</v>
       </c>
       <c r="R5" t="n">
-        <v>6525428</v>
+        <v>6525430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121407557</v>
       </c>
       <c r="B2" t="n">
-        <v>91269</v>
+        <v>91270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121498378</v>
       </c>
       <c r="B3" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>121498381</v>
       </c>
       <c r="B4" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>121498382</v>
       </c>
       <c r="B5" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498378</v>
+        <v>121498381</v>
       </c>
       <c r="B3" t="n">
         <v>90740</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621889</v>
+        <v>621849</v>
       </c>
       <c r="R3" t="n">
-        <v>6525447</v>
+        <v>6525428</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498381</v>
+        <v>121498382</v>
       </c>
       <c r="B4" t="n">
         <v>90740</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621849</v>
+        <v>621850</v>
       </c>
       <c r="R4" t="n">
-        <v>6525428</v>
+        <v>6525430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498382</v>
+        <v>121498378</v>
       </c>
       <c r="B5" t="n">
         <v>90740</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621850</v>
+        <v>621889</v>
       </c>
       <c r="R5" t="n">
-        <v>6525430</v>
+        <v>6525447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498381</v>
+        <v>121498382</v>
       </c>
       <c r="B3" t="n">
         <v>90740</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621849</v>
+        <v>621850</v>
       </c>
       <c r="R3" t="n">
-        <v>6525428</v>
+        <v>6525430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498382</v>
+        <v>121498378</v>
       </c>
       <c r="B4" t="n">
         <v>90740</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621850</v>
+        <v>621889</v>
       </c>
       <c r="R4" t="n">
-        <v>6525430</v>
+        <v>6525447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498378</v>
+        <v>121498381</v>
       </c>
       <c r="B5" t="n">
         <v>90740</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621889</v>
+        <v>621849</v>
       </c>
       <c r="R5" t="n">
-        <v>6525447</v>
+        <v>6525428</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498382</v>
+        <v>121498378</v>
       </c>
       <c r="B3" t="n">
         <v>90740</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621850</v>
+        <v>621889</v>
       </c>
       <c r="R3" t="n">
-        <v>6525430</v>
+        <v>6525447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498378</v>
+        <v>121498381</v>
       </c>
       <c r="B4" t="n">
         <v>90740</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621889</v>
+        <v>621849</v>
       </c>
       <c r="R4" t="n">
-        <v>6525447</v>
+        <v>6525428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498381</v>
+        <v>121498382</v>
       </c>
       <c r="B5" t="n">
         <v>90740</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621849</v>
+        <v>621850</v>
       </c>
       <c r="R5" t="n">
-        <v>6525428</v>
+        <v>6525430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121407557</v>
       </c>
       <c r="B2" t="n">
-        <v>91270</v>
+        <v>91278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498378</v>
+        <v>121498382</v>
       </c>
       <c r="B3" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621889</v>
+        <v>621850</v>
       </c>
       <c r="R3" t="n">
-        <v>6525447</v>
+        <v>6525430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498381</v>
+        <v>121498378</v>
       </c>
       <c r="B4" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621849</v>
+        <v>621889</v>
       </c>
       <c r="R4" t="n">
-        <v>6525428</v>
+        <v>6525447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498382</v>
+        <v>121498381</v>
       </c>
       <c r="B5" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621850</v>
+        <v>621849</v>
       </c>
       <c r="R5" t="n">
-        <v>6525430</v>
+        <v>6525428</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498378</v>
+        <v>121498382</v>
       </c>
       <c r="B3" t="n">
         <v>90748</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621889</v>
+        <v>621850</v>
       </c>
       <c r="R3" t="n">
-        <v>6525447</v>
+        <v>6525430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498382</v>
+        <v>121498378</v>
       </c>
       <c r="B4" t="n">
         <v>90748</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621850</v>
+        <v>621889</v>
       </c>
       <c r="R4" t="n">
-        <v>6525430</v>
+        <v>6525447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 56113-2024 artfynd.xlsx
+++ b/artfynd/A 56113-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121498382</v>
+        <v>121498378</v>
       </c>
       <c r="B3" t="n">
         <v>90748</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621850</v>
+        <v>621889</v>
       </c>
       <c r="R3" t="n">
-        <v>6525430</v>
+        <v>6525447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121498378</v>
+        <v>121498381</v>
       </c>
       <c r="B4" t="n">
         <v>90748</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621889</v>
+        <v>621849</v>
       </c>
       <c r="R4" t="n">
-        <v>6525447</v>
+        <v>6525428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121498381</v>
+        <v>121498382</v>
       </c>
       <c r="B5" t="n">
         <v>90748</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621849</v>
+        <v>621850</v>
       </c>
       <c r="R5" t="n">
-        <v>6525428</v>
+        <v>6525430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
